--- a/docs/reports/WCR_Kavach_Unified_KPI_Jun15-Jun21.xlsx
+++ b/docs/reports/WCR_Kavach_Unified_KPI_Jun15-Jun21.xlsx
@@ -709,7 +709,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Period: 15 Jun - 21 Jun 2026  ·  all locomotives  ·  one combined row</t>
+          <t>Period: Jun15 - Jun21 (custom)  ·  all locomotives  ·  one combined row</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>15 Jun - 21 Jun 2026</t>
+          <t>Jun15 - Jun21 (custom)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -11590,7 +11590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11609,6 +11609,9 @@
     <col width="26" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="46" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11708,8 +11711,23 @@
           <t>Suspected Reason (undesirable)</t>
         </is>
       </c>
-    </row>
-    <row r="6">
+      <c r="Q5" s="14" t="inlineStr">
+        <is>
+          <t>Points/Track condition</t>
+        </is>
+      </c>
+      <c r="R5" s="14" t="inlineStr">
+        <is>
+          <t>Signal Aspect Analysis</t>
+        </is>
+      </c>
+      <c r="S5" s="14" t="inlineStr">
+        <is>
+          <t>Loco Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="289" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
         <is>
           <t>16 Jun</t>
@@ -11782,8 +11800,26 @@
           <t>-</t>
         </is>
       </c>
-    </row>
-    <row r="7">
+      <c r="Q6" s="33" t="inlineStr">
+        <is>
+          <t>Route: entry ? → exit SV28.
+Condition: no interlocked route resolved at this approach — points/tracks not determined.
+Loco: loco 138 m short of SV28 (sig abs 918828); EB onset 14:49:24 at 55 km/h @ abs 918966 (138 m before SV28); halt 14:50:00 @ abs 918801 (27 m past SV28).</t>
+        </is>
+      </c>
+      <c r="R6" s="33" t="inlineStr">
+        <is>
+          <t>• At 14:49:03:240, the approach signal SV28 was displaying BLANK (BLANK) in the field but YELLOW (Y) on the DMI — a field/DMI aspect mismatch.
+• At 14:49:08 on 16/06/2026, the approach signal SV28 showed RED (R) in the field / RED (R) on the DMI (field and DMI agree).</t>
+        </is>
+      </c>
+      <c r="S6" s="31" t="inlineStr">
+        <is>
+          <t>Medha/Kernex</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="274" customHeight="1">
       <c r="A7" s="31" t="inlineStr">
         <is>
           <t>16 Jun</t>
@@ -11843,7 +11879,7 @@
       </c>
       <c r="N7" s="33" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O7" s="31" t="inlineStr">
@@ -11856,8 +11892,26 @@
           <t>EB at 0-1 km/h</t>
         </is>
       </c>
-    </row>
-    <row r="8">
+      <c r="Q7" s="33" t="inlineStr">
+        <is>
+          <t>Route: entry ? → exit S2.
+Condition: no interlocked route resolved at this approach — points/tracks not determined.
+Loco: loco 950 m short of S2 (sig abs 917851); EB onset 14:51:28 at 0 km/h @ abs 918801 (950 m before S2); halt 14:51:28 @ abs 918801 (950 m before S2).</t>
+        </is>
+      </c>
+      <c r="R7" s="33" t="inlineStr">
+        <is>
+          <t>• At 14:40:15:583, the approach signal S2 was displaying GREEN (G) in the field but RED (R) on the DMI — a field/DMI aspect mismatch.
+• At 14:49:50 on 16/06/2026, the approach signal S2 showed GREEN (G) in the field / GREEN (G) on the DMI (field and DMI agree).</t>
+        </is>
+      </c>
+      <c r="S7" s="31" t="inlineStr">
+        <is>
+          <t>Medha/Kernex</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="289" customHeight="1">
       <c r="A8" s="31" t="inlineStr">
         <is>
           <t>16 Jun</t>
@@ -11930,8 +11984,26 @@
           <t>-</t>
         </is>
       </c>
-    </row>
-    <row r="9">
+      <c r="Q8" s="33" t="inlineStr">
+        <is>
+          <t>Route: entry ? → exit SV28.
+Condition: no interlocked route resolved at this approach — points/tracks not determined.
+Loco: loco 119 m short of SV28 (sig abs 918828); EB onset 18:29:06 at 52 km/h @ abs 918947 (119 m before SV28); halt 18:29:30 @ abs 918821 (7 m past SV28).</t>
+        </is>
+      </c>
+      <c r="R8" s="33" t="inlineStr">
+        <is>
+          <t>• At 18:28:49:436, the approach signal SV28 was displaying BLANK (BLANK) in the field but YELLOW (Y) on the DMI — a field/DMI aspect mismatch.
+• At 18:28:55 on 16/06/2026, the approach signal SV28 showed RED (R) in the field / RED (R) on the DMI (field and DMI agree).</t>
+        </is>
+      </c>
+      <c r="S8" s="31" t="inlineStr">
+        <is>
+          <t>Medha/Kernex</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="439" customHeight="1">
       <c r="A9" s="31" t="inlineStr">
         <is>
           <t>16 Jun</t>
@@ -12004,8 +12076,27 @@
           <t>EB at 0-1 km/h</t>
         </is>
       </c>
-    </row>
-    <row r="10">
+      <c r="Q9" s="33" t="inlineStr">
+        <is>
+          <t>Route: entry S28 → exit S2 (EntrySigId 9 / ExitSigId 11).
+Condition: route clear — points P231/232, P225/226, P223/224, P221/222, P217/218, P209/210 (favourable/free).
+FIU contacts: point P231/232 (c94) P→favourable; point P225/226 (c90) P→favourable; point P223/224 (c88) P→favourable; point P221/222 (c86) P→favourable; point P217/218 (c84) P→favourable; point P209/210 (c80) P→favourable.
+Loco: loco 970 m short of S2 (sig abs 917851); EB onset 18:30:36 at 0 km/h @ abs 918821 (970 m before S2); halt 18:30:36 @ abs 918821 (970 m before S2).</t>
+        </is>
+      </c>
+      <c r="R9" s="33" t="inlineStr">
+        <is>
+          <t>• At 18:02:13:699, the ahead signal S2 was displaying GREEN (G) in the field but RED (R) on the DMI — a field/DMI aspect mismatch.
+• At 18:29:22:330, the approach signal S28 was displaying GREEN (G) in the field but RED (R) on the DMI — a field/DMI aspect mismatch.</t>
+        </is>
+      </c>
+      <c r="S9" s="31" t="inlineStr">
+        <is>
+          <t>Medha/Kernex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="439" customHeight="1">
       <c r="A10" s="31" t="inlineStr">
         <is>
           <t>16 Jun</t>
@@ -12065,7 +12156,7 @@
       </c>
       <c r="N10" s="33" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O10" s="31" t="inlineStr">
@@ -12078,8 +12169,27 @@
           <t>EB at 0-1 km/h</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="49" customHeight="1">
+      <c r="Q10" s="33" t="inlineStr">
+        <is>
+          <t>Route: entry S28 → exit S2 (EntrySigId 9 / ExitSigId 11).
+Condition: route clear — points P231/232, P225/226, P223/224, P221/222, P217/218, P209/210 (favourable/free).
+FIU contacts: point P231/232 (c94) P→favourable; point P225/226 (c90) P→favourable; point P223/224 (c88) P→favourable; point P221/222 (c86) P→favourable; point P217/218 (c84) P→favourable; point P209/210 (c80) P→favourable.
+Loco: loco 970 m short of S2 (sig abs 917851); EB onset 18:31:24 at 0 km/h @ abs 918821 (970 m before S2); halt 18:31:26 @ abs 918821 (970 m before S2).</t>
+        </is>
+      </c>
+      <c r="R10" s="33" t="inlineStr">
+        <is>
+          <t>• At 18:02:13:699, the ahead signal S2 was displaying GREEN (G) in the field but RED (R) on the DMI — a field/DMI aspect mismatch.
+• At 18:29:22:330, the approach signal S28 was displaying GREEN (G) in the field but RED (R) on the DMI — a field/DMI aspect mismatch.</t>
+        </is>
+      </c>
+      <c r="S10" s="31" t="inlineStr">
+        <is>
+          <t>Medha/Kernex</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="439" customHeight="1">
       <c r="A11" s="31" t="inlineStr">
         <is>
           <t>17 Jun</t>
@@ -12153,8 +12263,26 @@
           <t>PG issue (speed fluctuation); Trip mode</t>
         </is>
       </c>
-    </row>
-    <row r="12">
+      <c r="Q11" s="33" t="inlineStr">
+        <is>
+          <t>Route: entry S28 → exit S2 (EntrySigId 9 / ExitSigId 11).
+Condition: route clear — points P231/232, P225/226, P223/224, P221/222, P217/218, P209/210 (favourable/free).
+FIU contacts: point P231/232 (c94) P→favourable; point P225/226 (c90) P→favourable; point P223/224 (c88) P→favourable; point P221/222 (c86) P→favourable; point P217/218 (c84) P→favourable; point P209/210 (c80) P→favourable.
+Loco: loco 973 m short of S2 (sig abs 917851); EB onset 00:01:20 at 4 km/h @ abs 918824 (973 m before S2); halt 00:01:56 @ abs 918824 (973 m before S2).</t>
+        </is>
+      </c>
+      <c r="R11" s="33" t="inlineStr">
+        <is>
+          <t>@ 00:00:04 on 17/06/2026: S28 (col 9): field GREEN (G), DMI GREEN (G); S2 (col 11): field GREEN (G), DMI GREEN (G)</t>
+        </is>
+      </c>
+      <c r="S11" s="31" t="inlineStr">
+        <is>
+          <t>Medha/Kernex</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="439" customHeight="1">
       <c r="A12" s="31" t="inlineStr">
         <is>
           <t>17 Jun</t>
@@ -12227,8 +12355,26 @@
           <t>EB at 0-1 km/h</t>
         </is>
       </c>
-    </row>
-    <row r="13">
+      <c r="Q12" s="33" t="inlineStr">
+        <is>
+          <t>Route: entry S28 → exit S2 (EntrySigId 9 / ExitSigId 11).
+Condition: route clear — points P231/232, P225/226, P223/224, P221/222, P217/218, P209/210 (favourable/free).
+FIU contacts: point P231/232 (c94) P→favourable; point P225/226 (c90) P→favourable; point P223/224 (c88) P→favourable; point P221/222 (c86) P→favourable; point P217/218 (c84) P→favourable; point P209/210 (c80) P→favourable.
+Loco: loco 973 m short of S2 (sig abs 917851); EB onset 00:03:10 at 0 km/h @ abs 918824 (973 m before S2); halt 00:03:10 @ abs 918824 (973 m before S2).</t>
+        </is>
+      </c>
+      <c r="R12" s="33" t="inlineStr">
+        <is>
+          <t>• At 00:01:21:551, the approach signal S28 was displaying GREEN (G) in the field but RED (R) on the DMI — a field/DMI aspect mismatch.</t>
+        </is>
+      </c>
+      <c r="S12" s="31" t="inlineStr">
+        <is>
+          <t>Medha/Kernex</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="229" customHeight="1">
       <c r="A13" s="31" t="inlineStr">
         <is>
           <t>18 Jun</t>
@@ -12301,8 +12447,25 @@
           <t>EB at 0-1 km/h; Shunting mode</t>
         </is>
       </c>
-    </row>
-    <row r="14">
+      <c r="Q13" s="33" t="inlineStr">
+        <is>
+          <t>Route: entry ? → exit S44.
+Condition: no interlocked route resolved at this approach — points/tracks not determined.
+Loco: loco 869 m short of S44 (sig abs 1028164); EB onset 02:15:04 at 0 km/h @ abs 1029033 (869 m before S44); halt 02:16:34 @ abs 1029033 (869 m before S44).</t>
+        </is>
+      </c>
+      <c r="R13" s="33" t="inlineStr">
+        <is>
+          <t>• At 02:14:31 on 18/06/2026, the approach signal S44 showed RED (R) in the field / RED (R) on the DMI (field and DMI agree).</t>
+        </is>
+      </c>
+      <c r="S13" s="31" t="inlineStr">
+        <is>
+          <t>HBL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="304" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
           <t>19 Jun</t>
@@ -12375,8 +12538,26 @@
           <t>-</t>
         </is>
       </c>
-    </row>
-    <row r="15">
+      <c r="Q14" s="36" t="inlineStr">
+        <is>
+          <t>Route: entry ? → exit UPGATEINNDIST.
+Condition: no interlocked route resolved at this approach — points/tracks not determined.
+Loco: loco 1253 m short of UPGATEINNDIST (sig abs 1167280); EB onset 06:42:00 at 77 km/h @ abs 1166027 (1253 m before UPGATEINNDIST); halt 06:42:00 @ abs 1166027 (1253 m before UPGATEINNDIST).</t>
+        </is>
+      </c>
+      <c r="R14" s="36" t="inlineStr">
+        <is>
+          <t>• At 06:09:41:425, the approach signal UPGATEINNDIST was displaying GREEN (G) in the field but YELLOW (Y) on the DMI — a field/DMI aspect mismatch.
+• At 06:41:59 on 19/06/2026, the approach signal UPGATEINNDIST showed YELLOW (Y) in the field / YELLOW (Y) on the DMI (field and DMI agree).</t>
+        </is>
+      </c>
+      <c r="S14" s="16" t="inlineStr">
+        <is>
+          <t>Medha/Kernex</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="184" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
           <t>19 Jun</t>
@@ -12449,8 +12630,25 @@
           <t>FS-&gt;SR degradation + EB</t>
         </is>
       </c>
-    </row>
-    <row r="16">
+      <c r="Q15" s="36" t="inlineStr">
+        <is>
+          <t>Route: entry ? → exit SV28.
+Condition: no interlocked route resolved at this approach — points/tracks not determined.
+Loco: loco 1667 m short of SV28 (sig abs 918828); EB onset 11:04:08 at 21 km/h; halt 11:04:18.</t>
+        </is>
+      </c>
+      <c r="R15" s="36" t="inlineStr">
+        <is>
+          <t>• At 11:03:06 on 19/06/2026, the approach signal SV28 showed GREEN (G) in the field / GREEN (G) on the DMI (field and DMI agree).</t>
+        </is>
+      </c>
+      <c r="S15" s="16" t="inlineStr">
+        <is>
+          <t>Medha/Kernex</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="304" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
           <t>19 Jun</t>
@@ -12510,7 +12708,7 @@
       </c>
       <c r="N16" s="36" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="O16" s="16" t="inlineStr">
@@ -12523,8 +12721,26 @@
           <t>Failure mode</t>
         </is>
       </c>
-    </row>
-    <row r="17">
+      <c r="Q16" s="36" t="inlineStr">
+        <is>
+          <t>Route: entry ? → exit DNIBSSIGS50.
+Condition: no interlocked route resolved at this approach — points/tracks not determined.
+Loco: loco 203 m short of DNIBSSIGS50 (sig abs 1206836); EB onset 11:18:54 at 128 km/h @ abs 1206633 (203 m before DNIBSSIGS50); halt 11:19:40 @ abs 1207504 (668 m past DNIBSSIGS50).</t>
+        </is>
+      </c>
+      <c r="R16" s="36" t="inlineStr">
+        <is>
+          <t>• At 10:19:58:159, the approach signal DNIBSSIGS50 was displaying GREEN (G) in the field but RED (R) on the DMI — a field/DMI aspect mismatch.
+• At 11:12:20 on 19/06/2026, the approach signal DNIBSSIGS50 showed GREEN (G) in the field / GREEN (G) on the DMI (field and DMI agree).</t>
+        </is>
+      </c>
+      <c r="S16" s="16" t="inlineStr">
+        <is>
+          <t>Medha/Kernex</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="274" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
           <t>19 Jun</t>
@@ -12597,8 +12813,26 @@
           <t>Failure mode</t>
         </is>
       </c>
-    </row>
-    <row r="18">
+      <c r="Q17" s="36" t="inlineStr">
+        <is>
+          <t>Route: entry ? → exit SF1.
+Condition: no interlocked route resolved at this approach — points/tracks not determined.
+Loco: loco 511 m short of SF1 (sig abs 1137765); EB onset 18:46:58 at 124 km/h @ abs 1138276 (511 m before SF1); halt 18:47:42 @ abs 1137483 (282 m past SF1).</t>
+        </is>
+      </c>
+      <c r="R17" s="36" t="inlineStr">
+        <is>
+          <t>• At 18:44:40:522, the approach signal SF1 was displaying GREEN (G) in the field but RED (R) on the DMI — a field/DMI aspect mismatch.
+• At 18:44:50 on 19/06/2026, the approach signal SF1 showed GREEN (G) in the field / GREEN (G) on the DMI (field and DMI agree).</t>
+        </is>
+      </c>
+      <c r="S17" s="16" t="inlineStr">
+        <is>
+          <t>Medha/Kernex</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
       <c r="A18" s="31" t="inlineStr">
         <is>
           <t>20 Jun</t>
@@ -12671,8 +12905,23 @@
           <t>-</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="34" customHeight="1">
+      <c r="Q18" s="33" t="inlineStr">
+        <is>
+          <t>n/a (ahead signal not resolved)</t>
+        </is>
+      </c>
+      <c r="R18" s="33" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="S18" s="31" t="inlineStr">
+        <is>
+          <t>Medha/Kernex</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="229" customHeight="1">
       <c r="A19" s="31" t="inlineStr">
         <is>
           <t>20 Jun</t>
@@ -12746,8 +12995,25 @@
           <t>Sudden MA drop; Failure mode</t>
         </is>
       </c>
-    </row>
-    <row r="20">
+      <c r="Q19" s="33" t="inlineStr">
+        <is>
+          <t>Route: entry ? → exit S12.
+Condition: no interlocked route resolved at this approach — points/tracks not determined.
+Loco: loco 494 m short of S12 (sig abs 963991); EB onset 15:45:16 at 128 km/h @ abs 964485 (494 m before S12); halt 15:46:26 @ abs 963486 (505 m past S12).</t>
+        </is>
+      </c>
+      <c r="R19" s="33" t="inlineStr">
+        <is>
+          <t>• At 15:44:50 on 20/06/2026, the approach signal S12 showed GREEN (G) in the field / GREEN (G) on the DMI (field and DMI agree).</t>
+        </is>
+      </c>
+      <c r="S19" s="31" t="inlineStr">
+        <is>
+          <t>HBL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="244" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
           <t>20 Jun</t>
@@ -12820,8 +13086,25 @@
           <t>-</t>
         </is>
       </c>
-    </row>
-    <row r="21">
+      <c r="Q20" s="36" t="inlineStr">
+        <is>
+          <t>Route: entry ? → exit S45.
+Condition: no interlocked route resolved at this approach — points/tracks not determined.
+Loco: loco 1619 m short of S45 (sig abs 1028188); EB onset 21:11:08 at 33 km/h @ abs 1029807 (1619 m before S45); halt 21:11:22 @ abs 1029721 (1533 m before S45).</t>
+        </is>
+      </c>
+      <c r="R20" s="36" t="inlineStr">
+        <is>
+          <t>• At 21:10:43 on 20/06/2026, the approach signal S45 showed RED (R) in the field / RED (R) on the DMI (field and DMI agree).</t>
+        </is>
+      </c>
+      <c r="S20" s="16" t="inlineStr">
+        <is>
+          <t>Medha/Kernex</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="229" customHeight="1">
       <c r="A21" s="31" t="inlineStr">
         <is>
           <t>21 Jun</t>
@@ -12894,8 +13177,25 @@
           <t>Trip mode</t>
         </is>
       </c>
-    </row>
-    <row r="22">
+      <c r="Q21" s="33" t="inlineStr">
+        <is>
+          <t>Route: entry ? → exit S46.
+Condition: no interlocked route resolved at this approach — points/tracks not determined.
+Loco: loco 774 m short of S46 (sig abs 1028199); EB onset 09:30:00 at 9 km/h @ abs 1028973 (774 m before S46); halt 09:31:12 @ abs 1028978 (779 m before S46).</t>
+        </is>
+      </c>
+      <c r="R21" s="33" t="inlineStr">
+        <is>
+          <t>• At 09:27:09 on 21/06/2026, the approach signal S46 showed RED (R) in the field / RED (R) on the DMI (field and DMI agree).</t>
+        </is>
+      </c>
+      <c r="S21" s="31" t="inlineStr">
+        <is>
+          <t>Medha/Kernex</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
       <c r="A22" s="31" t="inlineStr">
         <is>
           <t>21 Jun</t>
@@ -12955,24 +13255,39 @@
       </c>
       <c r="N22" s="33" t="inlineStr">
         <is>
+          <t>7570</t>
+        </is>
+      </c>
+      <c r="O22" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P22" s="33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q22" s="33" t="inlineStr">
+        <is>
+          <t>n/a (ahead signal not resolved)</t>
+        </is>
+      </c>
+      <c r="R22" s="33" t="inlineStr">
+        <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="O22" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P22" s="33" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="S22" s="31" t="inlineStr">
+        <is>
+          <t>Medha/Kernex</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/reports/WCR_Kavach_Unified_KPI_Jun15-Jun21.xlsx
+++ b/docs/reports/WCR_Kavach_Unified_KPI_Jun15-Jun21.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -184,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -206,13 +206,13 @@
     <xf numFmtId="3" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -228,7 +228,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -243,7 +243,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -258,7 +258,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -308,6 +308,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -713,7 +731,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -856,19 +873,19 @@
         <f>'Daily Breakdown'!J266</f>
         <v/>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="46">
         <f>IFERROR(G5/D5,0)</f>
         <v/>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="47">
         <f>IFERROR(G5/E5,0)</f>
         <v/>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="48">
         <f>IFERROR(G5/E5*100,0)</f>
         <v/>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="47">
         <f>IFERROR(G5/(D5*E5/1000),0)</f>
         <v/>
       </c>
@@ -876,19 +893,19 @@
         <f>'Daily Breakdown'!K266</f>
         <v/>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="46">
         <f>IFERROR(N5/D5,0)</f>
         <v/>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="47">
         <f>IFERROR(N5/E5,0)</f>
         <v/>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="47">
         <f>IFERROR(N5/(D5*E5/100),0)</f>
         <v/>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="48">
         <f>IFERROR(N5/E5*100,0)</f>
         <v/>
       </c>
@@ -938,7 +955,13 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="37" t="inlineStr">
+        <is>
+          <t>Availability base excludes locos with FS+OS pkts = 0 (they are still listed; only the Total-pkts availability base drops them).</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1010,7 +1033,7 @@
       <c r="C4" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="49" t="n">
         <v>543.84</v>
       </c>
       <c r="E4" s="18" t="n">
@@ -1050,7 +1073,7 @@
       <c r="C5" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="49" t="n">
         <v>541.63</v>
       </c>
       <c r="E5" s="18" t="n">
@@ -1090,7 +1113,7 @@
       <c r="C6" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="49" t="n">
         <v>543.75</v>
       </c>
       <c r="E6" s="18" t="n">
@@ -1130,7 +1153,7 @@
       <c r="C7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="49" t="n">
         <v>541.62</v>
       </c>
       <c r="E7" s="18" t="n">
@@ -1170,7 +1193,7 @@
       <c r="C8" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="49" t="n">
         <v>543.67</v>
       </c>
       <c r="E8" s="18" t="n">
@@ -1210,7 +1233,7 @@
       <c r="C9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="49" t="n">
         <v>252.09</v>
       </c>
       <c r="E9" s="18" t="n">
@@ -1250,7 +1273,7 @@
       <c r="C10" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="49" t="n">
         <v>252.18</v>
       </c>
       <c r="E10" s="18" t="n">
@@ -1290,7 +1313,7 @@
       <c r="C11" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="49" t="n">
         <v>329.88</v>
       </c>
       <c r="E11" s="18" t="n">
@@ -1330,7 +1353,7 @@
       <c r="C12" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="49" t="n">
         <v>470.59</v>
       </c>
       <c r="E12" s="18" t="n">
@@ -1370,7 +1393,7 @@
       <c r="C13" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="49" t="n">
         <v>386.43</v>
       </c>
       <c r="E13" s="18" t="n">
@@ -1410,7 +1433,7 @@
       <c r="C14" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="49" t="n">
         <v>464.15</v>
       </c>
       <c r="E14" s="18" t="n">
@@ -1450,7 +1473,7 @@
       <c r="C15" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="49" t="n">
         <v>510.93</v>
       </c>
       <c r="E15" s="18" t="n">
@@ -1490,7 +1513,7 @@
       <c r="C16" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="49" t="n">
         <v>321.73</v>
       </c>
       <c r="E16" s="18" t="n">
@@ -1530,7 +1553,7 @@
       <c r="C17" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="49" t="n">
         <v>252.92</v>
       </c>
       <c r="E17" s="18" t="n">
@@ -1570,7 +1593,7 @@
       <c r="C18" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="49" t="n">
         <v>319.18</v>
       </c>
       <c r="E18" s="18" t="n">
@@ -1610,7 +1633,7 @@
       <c r="C19" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="49" t="n">
         <v>108.66</v>
       </c>
       <c r="E19" s="18" t="n">
@@ -1650,7 +1673,7 @@
       <c r="C20" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="49" t="n">
         <v>192.11</v>
       </c>
       <c r="E20" s="18" t="n">
@@ -1690,7 +1713,7 @@
       <c r="C21" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="49" t="n">
         <v>318.78</v>
       </c>
       <c r="E21" s="18" t="n">
@@ -1730,7 +1753,7 @@
       <c r="C22" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="49" t="n">
         <v>329.91</v>
       </c>
       <c r="E22" s="18" t="n">
@@ -1770,7 +1793,7 @@
       <c r="C23" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="49" t="n">
         <v>320.11</v>
       </c>
       <c r="E23" s="18" t="n">
@@ -1810,7 +1833,7 @@
       <c r="C24" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="49" t="n">
         <v>221.56</v>
       </c>
       <c r="E24" s="18" t="n">
@@ -1850,7 +1873,7 @@
       <c r="C25" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="49" t="n">
         <v>231.17</v>
       </c>
       <c r="E25" s="18" t="n">
@@ -1890,7 +1913,7 @@
       <c r="C26" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="49" t="n">
         <v>322.12</v>
       </c>
       <c r="E26" s="18" t="n">
@@ -1930,7 +1953,7 @@
       <c r="C27" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="49" t="n">
         <v>130.83</v>
       </c>
       <c r="E27" s="18" t="n">
@@ -1970,7 +1993,7 @@
       <c r="C28" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="49" t="n">
         <v>107.53</v>
       </c>
       <c r="E28" s="18" t="n">
@@ -2010,7 +2033,7 @@
       <c r="C29" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="49" t="n">
         <v>60.4</v>
       </c>
       <c r="E29" s="18" t="n">
@@ -2050,7 +2073,7 @@
       <c r="C30" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="49" t="n">
         <v>51.05</v>
       </c>
       <c r="E30" s="18" t="n">
@@ -2090,7 +2113,7 @@
       <c r="C31" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="49" t="n">
         <v>106.16</v>
       </c>
       <c r="E31" s="18" t="n">
@@ -2130,7 +2153,7 @@
       <c r="C32" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="49" t="n">
         <v>35.88</v>
       </c>
       <c r="E32" s="18" t="n">
@@ -2170,7 +2193,7 @@
       <c r="C33" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="49" t="n">
         <v>24.44</v>
       </c>
       <c r="E33" s="18" t="n">
@@ -2210,7 +2233,7 @@
       <c r="C34" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="49" t="n">
         <v>30.66</v>
       </c>
       <c r="E34" s="18" t="n">
@@ -2250,7 +2273,7 @@
       <c r="C35" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D35" s="17" t="n">
+      <c r="D35" s="49" t="n">
         <v>30.52</v>
       </c>
       <c r="E35" s="18" t="n">
@@ -2290,7 +2313,7 @@
       <c r="C36" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D36" s="17" t="n">
+      <c r="D36" s="49" t="n">
         <v>70.3</v>
       </c>
       <c r="E36" s="18" t="n">
@@ -2330,7 +2353,7 @@
       <c r="C37" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D37" s="17" t="n">
+      <c r="D37" s="49" t="n">
         <v>35.41</v>
       </c>
       <c r="E37" s="18" t="n">
@@ -2370,7 +2393,7 @@
       <c r="C38" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="49" t="n">
         <v>2.44</v>
       </c>
       <c r="E38" s="18" t="n">
@@ -2410,7 +2433,7 @@
       <c r="C39" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D39" s="17" t="n">
+      <c r="D39" s="49" t="n">
         <v>328.28</v>
       </c>
       <c r="E39" s="18" t="n">
@@ -2450,7 +2473,7 @@
       <c r="C40" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D40" s="17" t="n">
+      <c r="D40" s="49" t="n">
         <v>0.99</v>
       </c>
       <c r="E40" s="18" t="n">
@@ -2490,7 +2513,7 @@
       <c r="C41" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D41" s="17" t="n">
+      <c r="D41" s="49" t="n">
         <v>112.92</v>
       </c>
       <c r="E41" s="18" t="n">
@@ -2530,7 +2553,7 @@
       <c r="C42" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D42" s="17" t="n">
+      <c r="D42" s="49" t="n">
         <v>7.31</v>
       </c>
       <c r="E42" s="18" t="n">
@@ -2571,7 +2594,7 @@
         <f>SUM(C4:C42)</f>
         <v/>
       </c>
-      <c r="D43" s="22">
+      <c r="D43" s="50">
         <f>SUM(D4:D42)</f>
         <v/>
       </c>
@@ -2580,7 +2603,7 @@
         <v/>
       </c>
       <c r="F43" s="23">
-        <f>SUM(F4:F42)</f>
+        <f>SUMIF(E4:E42,"&gt;0",F4:F42)</f>
         <v/>
       </c>
       <c r="G43" s="24">
@@ -2618,7 +2641,7 @@
       <c r="C44" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="17" t="n">
+      <c r="D44" s="49" t="n">
         <v>543.87</v>
       </c>
       <c r="E44" s="18" t="n">
@@ -2658,7 +2681,7 @@
       <c r="C45" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="17" t="n">
+      <c r="D45" s="49" t="n">
         <v>543.83</v>
       </c>
       <c r="E45" s="18" t="n">
@@ -2698,7 +2721,7 @@
       <c r="C46" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D46" s="17" t="n">
+      <c r="D46" s="49" t="n">
         <v>251.26</v>
       </c>
       <c r="E46" s="18" t="n">
@@ -2738,7 +2761,7 @@
       <c r="C47" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="17" t="n">
+      <c r="D47" s="49" t="n">
         <v>473.44</v>
       </c>
       <c r="E47" s="18" t="n">
@@ -2778,7 +2801,7 @@
       <c r="C48" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D48" s="17" t="n">
+      <c r="D48" s="49" t="n">
         <v>321.5</v>
       </c>
       <c r="E48" s="18" t="n">
@@ -2818,7 +2841,7 @@
       <c r="C49" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D49" s="17" t="n">
+      <c r="D49" s="49" t="n">
         <v>513.86</v>
       </c>
       <c r="E49" s="18" t="n">
@@ -2858,7 +2881,7 @@
       <c r="C50" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D50" s="17" t="n">
+      <c r="D50" s="49" t="n">
         <v>458.39</v>
       </c>
       <c r="E50" s="18" t="n">
@@ -2898,7 +2921,7 @@
       <c r="C51" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D51" s="17" t="n">
+      <c r="D51" s="49" t="n">
         <v>246.56</v>
       </c>
       <c r="E51" s="18" t="n">
@@ -2938,7 +2961,7 @@
       <c r="C52" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D52" s="17" t="n">
+      <c r="D52" s="49" t="n">
         <v>518.27</v>
       </c>
       <c r="E52" s="18" t="n">
@@ -2978,7 +3001,7 @@
       <c r="C53" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D53" s="17" t="n">
+      <c r="D53" s="49" t="n">
         <v>329.84</v>
       </c>
       <c r="E53" s="18" t="n">
@@ -3018,7 +3041,7 @@
       <c r="C54" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D54" s="17" t="n">
+      <c r="D54" s="49" t="n">
         <v>323.24</v>
       </c>
       <c r="E54" s="18" t="n">
@@ -3058,7 +3081,7 @@
       <c r="C55" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D55" s="17" t="n">
+      <c r="D55" s="49" t="n">
         <v>324.35</v>
       </c>
       <c r="E55" s="18" t="n">
@@ -3098,7 +3121,7 @@
       <c r="C56" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D56" s="17" t="n">
+      <c r="D56" s="49" t="n">
         <v>319.24</v>
       </c>
       <c r="E56" s="18" t="n">
@@ -3138,7 +3161,7 @@
       <c r="C57" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D57" s="17" t="n">
+      <c r="D57" s="49" t="n">
         <v>322.47</v>
       </c>
       <c r="E57" s="18" t="n">
@@ -3178,7 +3201,7 @@
       <c r="C58" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D58" s="17" t="n">
+      <c r="D58" s="49" t="n">
         <v>330.14</v>
       </c>
       <c r="E58" s="18" t="n">
@@ -3218,7 +3241,7 @@
       <c r="C59" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D59" s="17" t="n">
+      <c r="D59" s="49" t="n">
         <v>237.38</v>
       </c>
       <c r="E59" s="18" t="n">
@@ -3258,7 +3281,7 @@
       <c r="C60" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D60" s="17" t="n">
+      <c r="D60" s="49" t="n">
         <v>318.81</v>
       </c>
       <c r="E60" s="18" t="n">
@@ -3298,7 +3321,7 @@
       <c r="C61" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D61" s="17" t="n">
+      <c r="D61" s="49" t="n">
         <v>163.05</v>
       </c>
       <c r="E61" s="18" t="n">
@@ -3338,7 +3361,7 @@
       <c r="C62" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D62" s="17" t="n">
+      <c r="D62" s="49" t="n">
         <v>243.15</v>
       </c>
       <c r="E62" s="18" t="n">
@@ -3378,7 +3401,7 @@
       <c r="C63" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D63" s="17" t="n">
+      <c r="D63" s="49" t="n">
         <v>170.69</v>
       </c>
       <c r="E63" s="18" t="n">
@@ -3418,7 +3441,7 @@
       <c r="C64" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D64" s="17" t="n">
+      <c r="D64" s="49" t="n">
         <v>108.54</v>
       </c>
       <c r="E64" s="18" t="n">
@@ -3458,7 +3481,7 @@
       <c r="C65" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D65" s="17" t="n">
+      <c r="D65" s="49" t="n">
         <v>222.04</v>
       </c>
       <c r="E65" s="18" t="n">
@@ -3498,7 +3521,7 @@
       <c r="C66" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D66" s="17" t="n">
+      <c r="D66" s="49" t="n">
         <v>322.62</v>
       </c>
       <c r="E66" s="18" t="n">
@@ -3538,7 +3561,7 @@
       <c r="C67" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D67" s="17" t="n">
+      <c r="D67" s="49" t="n">
         <v>108.67</v>
       </c>
       <c r="E67" s="18" t="n">
@@ -3578,7 +3601,7 @@
       <c r="C68" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D68" s="17" t="n">
+      <c r="D68" s="49" t="n">
         <v>108.53</v>
       </c>
       <c r="E68" s="18" t="n">
@@ -3618,7 +3641,7 @@
       <c r="C69" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D69" s="17" t="n">
+      <c r="D69" s="49" t="n">
         <v>292.96</v>
       </c>
       <c r="E69" s="18" t="n">
@@ -3658,7 +3681,7 @@
       <c r="C70" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D70" s="17" t="n">
+      <c r="D70" s="49" t="n">
         <v>149.78</v>
       </c>
       <c r="E70" s="18" t="n">
@@ -3698,7 +3721,7 @@
       <c r="C71" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D71" s="17" t="n">
+      <c r="D71" s="49" t="n">
         <v>160.94</v>
       </c>
       <c r="E71" s="18" t="n">
@@ -3738,7 +3761,7 @@
       <c r="C72" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D72" s="17" t="n">
+      <c r="D72" s="49" t="n">
         <v>120.19</v>
       </c>
       <c r="E72" s="18" t="n">
@@ -3778,7 +3801,7 @@
       <c r="C73" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D73" s="17" t="n">
+      <c r="D73" s="49" t="n">
         <v>110.39</v>
       </c>
       <c r="E73" s="18" t="n">
@@ -3818,7 +3841,7 @@
       <c r="C74" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D74" s="17" t="n">
+      <c r="D74" s="49" t="n">
         <v>13</v>
       </c>
       <c r="E74" s="18" t="n">
@@ -3858,7 +3881,7 @@
       <c r="C75" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D75" s="17" t="n">
+      <c r="D75" s="49" t="n">
         <v>106.78</v>
       </c>
       <c r="E75" s="18" t="n">
@@ -3898,7 +3921,7 @@
       <c r="C76" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D76" s="17" t="n">
+      <c r="D76" s="49" t="n">
         <v>14.25</v>
       </c>
       <c r="E76" s="18" t="n">
@@ -3938,7 +3961,7 @@
       <c r="C77" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D77" s="17" t="n">
+      <c r="D77" s="49" t="n">
         <v>42.7</v>
       </c>
       <c r="E77" s="18" t="n">
@@ -3978,7 +4001,7 @@
       <c r="C78" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D78" s="17" t="n">
+      <c r="D78" s="49" t="n">
         <v>34.59</v>
       </c>
       <c r="E78" s="18" t="n">
@@ -4018,7 +4041,7 @@
       <c r="C79" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D79" s="17" t="n">
+      <c r="D79" s="49" t="n">
         <v>99.95</v>
       </c>
       <c r="E79" s="18" t="n">
@@ -4058,7 +4081,7 @@
       <c r="C80" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D80" s="17" t="n">
+      <c r="D80" s="49" t="n">
         <v>25.3</v>
       </c>
       <c r="E80" s="18" t="n">
@@ -4098,7 +4121,7 @@
       <c r="C81" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D81" s="17" t="n">
+      <c r="D81" s="49" t="n">
         <v>13.58</v>
       </c>
       <c r="E81" s="18" t="n">
@@ -4138,7 +4161,7 @@
       <c r="C82" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D82" s="17" t="n">
+      <c r="D82" s="49" t="n">
         <v>31.12</v>
       </c>
       <c r="E82" s="18" t="n">
@@ -4178,7 +4201,7 @@
       <c r="C83" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D83" s="17" t="n">
+      <c r="D83" s="49" t="n">
         <v>510.19</v>
       </c>
       <c r="E83" s="18" t="n">
@@ -4219,7 +4242,7 @@
         <f>SUM(C44:C83)</f>
         <v/>
       </c>
-      <c r="D84" s="22">
+      <c r="D84" s="50">
         <f>SUM(D44:D83)</f>
         <v/>
       </c>
@@ -4228,7 +4251,7 @@
         <v/>
       </c>
       <c r="F84" s="23">
-        <f>SUM(F44:F83)</f>
+        <f>SUMIF(E44:E83,"&gt;0",F44:F83)</f>
         <v/>
       </c>
       <c r="G84" s="24">
@@ -4266,7 +4289,7 @@
       <c r="C85" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D85" s="17" t="n">
+      <c r="D85" s="49" t="n">
         <v>543.65</v>
       </c>
       <c r="E85" s="18" t="n">
@@ -4306,7 +4329,7 @@
       <c r="C86" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D86" s="17" t="n">
+      <c r="D86" s="49" t="n">
         <v>543.85</v>
       </c>
       <c r="E86" s="18" t="n">
@@ -4346,7 +4369,7 @@
       <c r="C87" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D87" s="17" t="n">
+      <c r="D87" s="49" t="n">
         <v>543.88</v>
       </c>
       <c r="E87" s="18" t="n">
@@ -4386,7 +4409,7 @@
       <c r="C88" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D88" s="17" t="n">
+      <c r="D88" s="49" t="n">
         <v>541.65</v>
       </c>
       <c r="E88" s="18" t="n">
@@ -4426,7 +4449,7 @@
       <c r="C89" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D89" s="17" t="n">
+      <c r="D89" s="49" t="n">
         <v>543.85</v>
       </c>
       <c r="E89" s="18" t="n">
@@ -4466,7 +4489,7 @@
       <c r="C90" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D90" s="17" t="n">
+      <c r="D90" s="49" t="n">
         <v>543.89</v>
       </c>
       <c r="E90" s="18" t="n">
@@ -4506,7 +4529,7 @@
       <c r="C91" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D91" s="17" t="n">
+      <c r="D91" s="49" t="n">
         <v>543.84</v>
       </c>
       <c r="E91" s="18" t="n">
@@ -4546,7 +4569,7 @@
       <c r="C92" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D92" s="17" t="n">
+      <c r="D92" s="49" t="n">
         <v>251.78</v>
       </c>
       <c r="E92" s="18" t="n">
@@ -4586,7 +4609,7 @@
       <c r="C93" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D93" s="17" t="n">
+      <c r="D93" s="49" t="n">
         <v>329.84</v>
       </c>
       <c r="E93" s="18" t="n">
@@ -4626,7 +4649,7 @@
       <c r="C94" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D94" s="17" t="n">
+      <c r="D94" s="49" t="n">
         <v>322.6</v>
       </c>
       <c r="E94" s="18" t="n">
@@ -4666,7 +4689,7 @@
       <c r="C95" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D95" s="17" t="n">
+      <c r="D95" s="49" t="n">
         <v>321.5</v>
       </c>
       <c r="E95" s="18" t="n">
@@ -4706,7 +4729,7 @@
       <c r="C96" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D96" s="17" t="n">
+      <c r="D96" s="49" t="n">
         <v>380.91</v>
       </c>
       <c r="E96" s="18" t="n">
@@ -4746,7 +4769,7 @@
       <c r="C97" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D97" s="17" t="n">
+      <c r="D97" s="49" t="n">
         <v>251.14</v>
       </c>
       <c r="E97" s="18" t="n">
@@ -4786,7 +4809,7 @@
       <c r="C98" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D98" s="17" t="n">
+      <c r="D98" s="49" t="n">
         <v>473.41</v>
       </c>
       <c r="E98" s="18" t="n">
@@ -4826,7 +4849,7 @@
       <c r="C99" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D99" s="17" t="n">
+      <c r="D99" s="49" t="n">
         <v>108.24</v>
       </c>
       <c r="E99" s="18" t="n">
@@ -4866,7 +4889,7 @@
       <c r="C100" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D100" s="17" t="n">
+      <c r="D100" s="49" t="n">
         <v>345.41</v>
       </c>
       <c r="E100" s="18" t="n">
@@ -4906,7 +4929,7 @@
       <c r="C101" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D101" s="17" t="n">
+      <c r="D101" s="49" t="n">
         <v>320.05</v>
       </c>
       <c r="E101" s="18" t="n">
@@ -4946,7 +4969,7 @@
       <c r="C102" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D102" s="17" t="n">
+      <c r="D102" s="49" t="n">
         <v>329.84</v>
       </c>
       <c r="E102" s="18" t="n">
@@ -4986,7 +5009,7 @@
       <c r="C103" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D103" s="17" t="n">
+      <c r="D103" s="49" t="n">
         <v>329.91</v>
       </c>
       <c r="E103" s="18" t="n">
@@ -5026,7 +5049,7 @@
       <c r="C104" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D104" s="17" t="n">
+      <c r="D104" s="49" t="n">
         <v>321.7</v>
       </c>
       <c r="E104" s="18" t="n">
@@ -5066,7 +5089,7 @@
       <c r="C105" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D105" s="17" t="n">
+      <c r="D105" s="49" t="n">
         <v>319.57</v>
       </c>
       <c r="E105" s="18" t="n">
@@ -5106,7 +5129,7 @@
       <c r="C106" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D106" s="17" t="n">
+      <c r="D106" s="49" t="n">
         <v>319.1</v>
       </c>
       <c r="E106" s="18" t="n">
@@ -5146,7 +5169,7 @@
       <c r="C107" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D107" s="17" t="n">
+      <c r="D107" s="49" t="n">
         <v>192.18</v>
       </c>
       <c r="E107" s="18" t="n">
@@ -5186,7 +5209,7 @@
       <c r="C108" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D108" s="17" t="n">
+      <c r="D108" s="49" t="n">
         <v>319.23</v>
       </c>
       <c r="E108" s="18" t="n">
@@ -5226,7 +5249,7 @@
       <c r="C109" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D109" s="17" t="n">
+      <c r="D109" s="49" t="n">
         <v>248.18</v>
       </c>
       <c r="E109" s="18" t="n">
@@ -5266,7 +5289,7 @@
       <c r="C110" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D110" s="17" t="n">
+      <c r="D110" s="49" t="n">
         <v>243.81</v>
       </c>
       <c r="E110" s="18" t="n">
@@ -5306,7 +5329,7 @@
       <c r="C111" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D111" s="17" t="n">
+      <c r="D111" s="49" t="n">
         <v>108.65</v>
       </c>
       <c r="E111" s="18" t="n">
@@ -5346,7 +5369,7 @@
       <c r="C112" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D112" s="17" t="n">
+      <c r="D112" s="49" t="n">
         <v>214.04</v>
       </c>
       <c r="E112" s="18" t="n">
@@ -5386,7 +5409,7 @@
       <c r="C113" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D113" s="17" t="n">
+      <c r="D113" s="49" t="n">
         <v>196.33</v>
       </c>
       <c r="E113" s="18" t="n">
@@ -5426,7 +5449,7 @@
       <c r="C114" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D114" s="17" t="n">
+      <c r="D114" s="49" t="n">
         <v>221.52</v>
       </c>
       <c r="E114" s="18" t="n">
@@ -5466,7 +5489,7 @@
       <c r="C115" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D115" s="17" t="n">
+      <c r="D115" s="49" t="n">
         <v>156.96</v>
       </c>
       <c r="E115" s="18" t="n">
@@ -5506,7 +5529,7 @@
       <c r="C116" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D116" s="17" t="n">
+      <c r="D116" s="49" t="n">
         <v>319.2</v>
       </c>
       <c r="E116" s="18" t="n">
@@ -5546,7 +5569,7 @@
       <c r="C117" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="17" t="n">
+      <c r="D117" s="49" t="n">
         <v>270.77</v>
       </c>
       <c r="E117" s="18" t="n">
@@ -5586,7 +5609,7 @@
       <c r="C118" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D118" s="17" t="n">
+      <c r="D118" s="49" t="n">
         <v>329.54</v>
       </c>
       <c r="E118" s="18" t="n">
@@ -5626,7 +5649,7 @@
       <c r="C119" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D119" s="17" t="n">
+      <c r="D119" s="49" t="n">
         <v>105.43</v>
       </c>
       <c r="E119" s="18" t="n">
@@ -5666,7 +5689,7 @@
       <c r="C120" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D120" s="17" t="n">
+      <c r="D120" s="49" t="n">
         <v>25.99</v>
       </c>
       <c r="E120" s="18" t="n">
@@ -5706,7 +5729,7 @@
       <c r="C121" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D121" s="17" t="n">
+      <c r="D121" s="49" t="n">
         <v>25.64</v>
       </c>
       <c r="E121" s="18" t="n">
@@ -5746,7 +5769,7 @@
       <c r="C122" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D122" s="17" t="n">
+      <c r="D122" s="49" t="n">
         <v>66.72</v>
       </c>
       <c r="E122" s="18" t="n">
@@ -5786,7 +5809,7 @@
       <c r="C123" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D123" s="17" t="n">
+      <c r="D123" s="49" t="n">
         <v>0.92</v>
       </c>
       <c r="E123" s="18" t="n">
@@ -5826,7 +5849,7 @@
       <c r="C124" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D124" s="17" t="n">
+      <c r="D124" s="49" t="n">
         <v>35.67</v>
       </c>
       <c r="E124" s="18" t="n">
@@ -5866,7 +5889,7 @@
       <c r="C125" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D125" s="17" t="n">
+      <c r="D125" s="49" t="n">
         <v>100.3</v>
       </c>
       <c r="E125" s="18" t="n">
@@ -5906,7 +5929,7 @@
       <c r="C126" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D126" s="17" t="n">
+      <c r="D126" s="49" t="n">
         <v>0.91</v>
       </c>
       <c r="E126" s="18" t="n">
@@ -5946,7 +5969,7 @@
       <c r="C127" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D127" s="17" t="n">
+      <c r="D127" s="49" t="n">
         <v>82.23</v>
       </c>
       <c r="E127" s="18" t="n">
@@ -5986,7 +6009,7 @@
       <c r="C128" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D128" s="17" t="n">
+      <c r="D128" s="49" t="n">
         <v>120.09</v>
       </c>
       <c r="E128" s="18" t="n">
@@ -6026,7 +6049,7 @@
       <c r="C129" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D129" s="17" t="n">
+      <c r="D129" s="49" t="n">
         <v>0.32</v>
       </c>
       <c r="E129" s="18" t="n">
@@ -6067,7 +6090,7 @@
         <f>SUM(C85:C129)</f>
         <v/>
       </c>
-      <c r="D130" s="22">
+      <c r="D130" s="50">
         <f>SUM(D85:D129)</f>
         <v/>
       </c>
@@ -6076,7 +6099,7 @@
         <v/>
       </c>
       <c r="F130" s="23">
-        <f>SUM(F85:F129)</f>
+        <f>SUMIF(E85:E129,"&gt;0",F85:F129)</f>
         <v/>
       </c>
       <c r="G130" s="24">
@@ -6114,7 +6137,7 @@
       <c r="C131" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D131" s="17" t="n">
+      <c r="D131" s="49" t="n">
         <v>543.88</v>
       </c>
       <c r="E131" s="18" t="n">
@@ -6154,7 +6177,7 @@
       <c r="C132" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D132" s="17" t="n">
+      <c r="D132" s="49" t="n">
         <v>543.63</v>
       </c>
       <c r="E132" s="18" t="n">
@@ -6194,7 +6217,7 @@
       <c r="C133" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D133" s="17" t="n">
+      <c r="D133" s="49" t="n">
         <v>543.86</v>
       </c>
       <c r="E133" s="18" t="n">
@@ -6234,7 +6257,7 @@
       <c r="C134" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D134" s="17" t="n">
+      <c r="D134" s="49" t="n">
         <v>251.86</v>
       </c>
       <c r="E134" s="18" t="n">
@@ -6274,7 +6297,7 @@
       <c r="C135" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D135" s="17" t="n">
+      <c r="D135" s="49" t="n">
         <v>251.81</v>
       </c>
       <c r="E135" s="18" t="n">
@@ -6314,7 +6337,7 @@
       <c r="C136" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D136" s="17" t="n">
+      <c r="D136" s="49" t="n">
         <v>469.92</v>
       </c>
       <c r="E136" s="18" t="n">
@@ -6354,7 +6377,7 @@
       <c r="C137" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D137" s="17" t="n">
+      <c r="D137" s="49" t="n">
         <v>512.53</v>
       </c>
       <c r="E137" s="18" t="n">
@@ -6394,7 +6417,7 @@
       <c r="C138" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D138" s="17" t="n">
+      <c r="D138" s="49" t="n">
         <v>515.66</v>
       </c>
       <c r="E138" s="18" t="n">
@@ -6434,7 +6457,7 @@
       <c r="C139" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D139" s="17" t="n">
+      <c r="D139" s="49" t="n">
         <v>470.59</v>
       </c>
       <c r="E139" s="18" t="n">
@@ -6474,7 +6497,7 @@
       <c r="C140" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D140" s="17" t="n">
+      <c r="D140" s="49" t="n">
         <v>108.67</v>
       </c>
       <c r="E140" s="18" t="n">
@@ -6514,7 +6537,7 @@
       <c r="C141" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D141" s="17" t="n">
+      <c r="D141" s="49" t="n">
         <v>322.6</v>
       </c>
       <c r="E141" s="18" t="n">
@@ -6554,7 +6577,7 @@
       <c r="C142" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D142" s="17" t="n">
+      <c r="D142" s="49" t="n">
         <v>321.74</v>
       </c>
       <c r="E142" s="18" t="n">
@@ -6594,7 +6617,7 @@
       <c r="C143" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D143" s="17" t="n">
+      <c r="D143" s="49" t="n">
         <v>329.09</v>
       </c>
       <c r="E143" s="18" t="n">
@@ -6634,7 +6657,7 @@
       <c r="C144" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D144" s="17" t="n">
+      <c r="D144" s="49" t="n">
         <v>318.8</v>
       </c>
       <c r="E144" s="18" t="n">
@@ -6674,7 +6697,7 @@
       <c r="C145" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D145" s="17" t="n">
+      <c r="D145" s="49" t="n">
         <v>294.19</v>
       </c>
       <c r="E145" s="18" t="n">
@@ -6714,7 +6737,7 @@
       <c r="C146" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D146" s="17" t="n">
+      <c r="D146" s="49" t="n">
         <v>319.22</v>
       </c>
       <c r="E146" s="18" t="n">
@@ -6754,7 +6777,7 @@
       <c r="C147" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D147" s="17" t="n">
+      <c r="D147" s="49" t="n">
         <v>198.5</v>
       </c>
       <c r="E147" s="18" t="n">
@@ -6794,7 +6817,7 @@
       <c r="C148" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D148" s="17" t="n">
+      <c r="D148" s="49" t="n">
         <v>108.61</v>
       </c>
       <c r="E148" s="18" t="n">
@@ -6834,7 +6857,7 @@
       <c r="C149" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D149" s="17" t="n">
+      <c r="D149" s="49" t="n">
         <v>297.9</v>
       </c>
       <c r="E149" s="18" t="n">
@@ -6874,7 +6897,7 @@
       <c r="C150" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D150" s="17" t="n">
+      <c r="D150" s="49" t="n">
         <v>102.14</v>
       </c>
       <c r="E150" s="18" t="n">
@@ -6914,7 +6937,7 @@
       <c r="C151" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D151" s="17" t="n">
+      <c r="D151" s="49" t="n">
         <v>121.82</v>
       </c>
       <c r="E151" s="18" t="n">
@@ -6954,7 +6977,7 @@
       <c r="C152" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D152" s="17" t="n">
+      <c r="D152" s="49" t="n">
         <v>68.31999999999999</v>
       </c>
       <c r="E152" s="18" t="n">
@@ -6994,7 +7017,7 @@
       <c r="C153" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D153" s="17" t="n">
+      <c r="D153" s="49" t="n">
         <v>42.96</v>
       </c>
       <c r="E153" s="18" t="n">
@@ -7034,7 +7057,7 @@
       <c r="C154" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D154" s="17" t="n">
+      <c r="D154" s="49" t="n">
         <v>100.78</v>
       </c>
       <c r="E154" s="18" t="n">
@@ -7074,7 +7097,7 @@
       <c r="C155" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D155" s="17" t="n">
+      <c r="D155" s="49" t="n">
         <v>3.68</v>
       </c>
       <c r="E155" s="18" t="n">
@@ -7114,7 +7137,7 @@
       <c r="C156" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D156" s="17" t="n">
+      <c r="D156" s="49" t="n">
         <v>11.93</v>
       </c>
       <c r="E156" s="18" t="n">
@@ -7154,7 +7177,7 @@
       <c r="C157" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D157" s="17" t="n">
+      <c r="D157" s="49" t="n">
         <v>25.72</v>
       </c>
       <c r="E157" s="18" t="n">
@@ -7194,7 +7217,7 @@
       <c r="C158" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D158" s="17" t="n">
+      <c r="D158" s="49" t="n">
         <v>9.32</v>
       </c>
       <c r="E158" s="18" t="n">
@@ -7234,7 +7257,7 @@
       <c r="C159" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D159" s="17" t="n">
+      <c r="D159" s="49" t="n">
         <v>428.04</v>
       </c>
       <c r="E159" s="18" t="n">
@@ -7274,7 +7297,7 @@
       <c r="C160" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D160" s="17" t="n">
+      <c r="D160" s="49" t="n">
         <v>50.65</v>
       </c>
       <c r="E160" s="18" t="n">
@@ -7314,7 +7337,7 @@
       <c r="C161" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D161" s="17" t="n">
+      <c r="D161" s="49" t="n">
         <v>510.18</v>
       </c>
       <c r="E161" s="18" t="n">
@@ -7355,7 +7378,7 @@
         <f>SUM(C131:C161)</f>
         <v/>
       </c>
-      <c r="D162" s="22">
+      <c r="D162" s="50">
         <f>SUM(D131:D161)</f>
         <v/>
       </c>
@@ -7364,7 +7387,7 @@
         <v/>
       </c>
       <c r="F162" s="23">
-        <f>SUM(F131:F161)</f>
+        <f>SUMIF(E131:E161,"&gt;0",F131:F161)</f>
         <v/>
       </c>
       <c r="G162" s="24">
@@ -7402,7 +7425,7 @@
       <c r="C163" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D163" s="17" t="n">
+      <c r="D163" s="49" t="n">
         <v>543.85</v>
       </c>
       <c r="E163" s="18" t="n">
@@ -7442,7 +7465,7 @@
       <c r="C164" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D164" s="17" t="n">
+      <c r="D164" s="49" t="n">
         <v>543.88</v>
       </c>
       <c r="E164" s="18" t="n">
@@ -7482,7 +7505,7 @@
       <c r="C165" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D165" s="17" t="n">
+      <c r="D165" s="49" t="n">
         <v>543.86</v>
       </c>
       <c r="E165" s="18" t="n">
@@ -7522,7 +7545,7 @@
       <c r="C166" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D166" s="17" t="n">
+      <c r="D166" s="49" t="n">
         <v>543.86</v>
       </c>
       <c r="E166" s="18" t="n">
@@ -7562,7 +7585,7 @@
       <c r="C167" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D167" s="17" t="n">
+      <c r="D167" s="49" t="n">
         <v>543.91</v>
       </c>
       <c r="E167" s="18" t="n">
@@ -7602,7 +7625,7 @@
       <c r="C168" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D168" s="17" t="n">
+      <c r="D168" s="49" t="n">
         <v>543.84</v>
       </c>
       <c r="E168" s="18" t="n">
@@ -7642,7 +7665,7 @@
       <c r="C169" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D169" s="17" t="n">
+      <c r="D169" s="49" t="n">
         <v>543.85</v>
       </c>
       <c r="E169" s="18" t="n">
@@ -7682,7 +7705,7 @@
       <c r="C170" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D170" s="17" t="n">
+      <c r="D170" s="49" t="n">
         <v>543.6</v>
       </c>
       <c r="E170" s="18" t="n">
@@ -7722,7 +7745,7 @@
       <c r="C171" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D171" s="17" t="n">
+      <c r="D171" s="49" t="n">
         <v>251.78</v>
       </c>
       <c r="E171" s="18" t="n">
@@ -7762,7 +7785,7 @@
       <c r="C172" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D172" s="17" t="n">
+      <c r="D172" s="49" t="n">
         <v>329.99</v>
       </c>
       <c r="E172" s="18" t="n">
@@ -7802,7 +7825,7 @@
       <c r="C173" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D173" s="17" t="n">
+      <c r="D173" s="49" t="n">
         <v>322.6</v>
       </c>
       <c r="E173" s="18" t="n">
@@ -7842,7 +7865,7 @@
       <c r="C174" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D174" s="17" t="n">
+      <c r="D174" s="49" t="n">
         <v>321.5</v>
       </c>
       <c r="E174" s="18" t="n">
@@ -7882,7 +7905,7 @@
       <c r="C175" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D175" s="17" t="n">
+      <c r="D175" s="49" t="n">
         <v>470.58</v>
       </c>
       <c r="E175" s="18" t="n">
@@ -7922,7 +7945,7 @@
       <c r="C176" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D176" s="17" t="n">
+      <c r="D176" s="49" t="n">
         <v>469.92</v>
       </c>
       <c r="E176" s="18" t="n">
@@ -7962,7 +7985,7 @@
       <c r="C177" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D177" s="17" t="n">
+      <c r="D177" s="49" t="n">
         <v>179.01</v>
       </c>
       <c r="E177" s="18" t="n">
@@ -8002,7 +8025,7 @@
       <c r="C178" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D178" s="17" t="n">
+      <c r="D178" s="49" t="n">
         <v>108.66</v>
       </c>
       <c r="E178" s="18" t="n">
@@ -8042,7 +8065,7 @@
       <c r="C179" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D179" s="17" t="n">
+      <c r="D179" s="49" t="n">
         <v>332.59</v>
       </c>
       <c r="E179" s="18" t="n">
@@ -8082,7 +8105,7 @@
       <c r="C180" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D180" s="17" t="n">
+      <c r="D180" s="49" t="n">
         <v>322.6</v>
       </c>
       <c r="E180" s="18" t="n">
@@ -8122,7 +8145,7 @@
       <c r="C181" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D181" s="17" t="n">
+      <c r="D181" s="49" t="n">
         <v>330.22</v>
       </c>
       <c r="E181" s="18" t="n">
@@ -8162,7 +8185,7 @@
       <c r="C182" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D182" s="17" t="n">
+      <c r="D182" s="49" t="n">
         <v>319.23</v>
       </c>
       <c r="E182" s="18" t="n">
@@ -8202,7 +8225,7 @@
       <c r="C183" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D183" s="17" t="n">
+      <c r="D183" s="49" t="n">
         <v>329.82</v>
       </c>
       <c r="E183" s="18" t="n">
@@ -8242,7 +8265,7 @@
       <c r="C184" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D184" s="17" t="n">
+      <c r="D184" s="49" t="n">
         <v>322.46</v>
       </c>
       <c r="E184" s="18" t="n">
@@ -8282,7 +8305,7 @@
       <c r="C185" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D185" s="17" t="n">
+      <c r="D185" s="49" t="n">
         <v>319.23</v>
       </c>
       <c r="E185" s="18" t="n">
@@ -8322,7 +8345,7 @@
       <c r="C186" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D186" s="17" t="n">
+      <c r="D186" s="49" t="n">
         <v>318.81</v>
       </c>
       <c r="E186" s="18" t="n">
@@ -8362,7 +8385,7 @@
       <c r="C187" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D187" s="17" t="n">
+      <c r="D187" s="49" t="n">
         <v>108.54</v>
       </c>
       <c r="E187" s="18" t="n">
@@ -8402,7 +8425,7 @@
       <c r="C188" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D188" s="17" t="n">
+      <c r="D188" s="49" t="n">
         <v>322.18</v>
       </c>
       <c r="E188" s="18" t="n">
@@ -8442,7 +8465,7 @@
       <c r="C189" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D189" s="17" t="n">
+      <c r="D189" s="49" t="n">
         <v>179.17</v>
       </c>
       <c r="E189" s="18" t="n">
@@ -8482,7 +8505,7 @@
       <c r="C190" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D190" s="17" t="n">
+      <c r="D190" s="49" t="n">
         <v>108.27</v>
       </c>
       <c r="E190" s="18" t="n">
@@ -8522,7 +8545,7 @@
       <c r="C191" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D191" s="17" t="n">
+      <c r="D191" s="49" t="n">
         <v>39.54</v>
       </c>
       <c r="E191" s="18" t="n">
@@ -8562,7 +8585,7 @@
       <c r="C192" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D192" s="17" t="n">
+      <c r="D192" s="49" t="n">
         <v>43.92</v>
       </c>
       <c r="E192" s="18" t="n">
@@ -8602,7 +8625,7 @@
       <c r="C193" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D193" s="17" t="n">
+      <c r="D193" s="49" t="n">
         <v>39.84</v>
       </c>
       <c r="E193" s="18" t="n">
@@ -8643,7 +8666,7 @@
         <f>SUM(C163:C193)</f>
         <v/>
       </c>
-      <c r="D194" s="22">
+      <c r="D194" s="50">
         <f>SUM(D163:D193)</f>
         <v/>
       </c>
@@ -8652,7 +8675,7 @@
         <v/>
       </c>
       <c r="F194" s="23">
-        <f>SUM(F163:F193)</f>
+        <f>SUMIF(E163:E193,"&gt;0",F163:F193)</f>
         <v/>
       </c>
       <c r="G194" s="24">
@@ -8690,7 +8713,7 @@
       <c r="C195" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D195" s="17" t="n">
+      <c r="D195" s="49" t="n">
         <v>543.88</v>
       </c>
       <c r="E195" s="18" t="n">
@@ -8730,7 +8753,7 @@
       <c r="C196" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D196" s="17" t="n">
+      <c r="D196" s="49" t="n">
         <v>543.87</v>
       </c>
       <c r="E196" s="18" t="n">
@@ -8770,7 +8793,7 @@
       <c r="C197" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D197" s="17" t="n">
+      <c r="D197" s="49" t="n">
         <v>541.64</v>
       </c>
       <c r="E197" s="18" t="n">
@@ -8810,7 +8833,7 @@
       <c r="C198" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D198" s="17" t="n">
+      <c r="D198" s="49" t="n">
         <v>541.58</v>
       </c>
       <c r="E198" s="18" t="n">
@@ -8850,7 +8873,7 @@
       <c r="C199" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D199" s="17" t="n">
+      <c r="D199" s="49" t="n">
         <v>543.88</v>
       </c>
       <c r="E199" s="18" t="n">
@@ -8890,7 +8913,7 @@
       <c r="C200" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D200" s="17" t="n">
+      <c r="D200" s="49" t="n">
         <v>543.86</v>
       </c>
       <c r="E200" s="18" t="n">
@@ -8930,7 +8953,7 @@
       <c r="C201" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D201" s="17" t="n">
+      <c r="D201" s="49" t="n">
         <v>543.65</v>
       </c>
       <c r="E201" s="18" t="n">
@@ -8970,7 +8993,7 @@
       <c r="C202" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D202" s="17" t="n">
+      <c r="D202" s="49" t="n">
         <v>330.04</v>
       </c>
       <c r="E202" s="18" t="n">
@@ -9010,7 +9033,7 @@
       <c r="C203" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D203" s="17" t="n">
+      <c r="D203" s="49" t="n">
         <v>108.66</v>
       </c>
       <c r="E203" s="18" t="n">
@@ -9050,7 +9073,7 @@
       <c r="C204" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D204" s="17" t="n">
+      <c r="D204" s="49" t="n">
         <v>322.61</v>
       </c>
       <c r="E204" s="18" t="n">
@@ -9090,7 +9113,7 @@
       <c r="C205" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D205" s="17" t="n">
+      <c r="D205" s="49" t="n">
         <v>470.59</v>
       </c>
       <c r="E205" s="18" t="n">
@@ -9130,7 +9153,7 @@
       <c r="C206" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D206" s="17" t="n">
+      <c r="D206" s="49" t="n">
         <v>251.9</v>
       </c>
       <c r="E206" s="18" t="n">
@@ -9170,7 +9193,7 @@
       <c r="C207" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D207" s="17" t="n">
+      <c r="D207" s="49" t="n">
         <v>471.64</v>
       </c>
       <c r="E207" s="18" t="n">
@@ -9210,7 +9233,7 @@
       <c r="C208" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D208" s="17" t="n">
+      <c r="D208" s="49" t="n">
         <v>321.44</v>
       </c>
       <c r="E208" s="18" t="n">
@@ -9250,7 +9273,7 @@
       <c r="C209" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D209" s="17" t="n">
+      <c r="D209" s="49" t="n">
         <v>470.59</v>
       </c>
       <c r="E209" s="18" t="n">
@@ -9290,7 +9313,7 @@
       <c r="C210" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D210" s="17" t="n">
+      <c r="D210" s="49" t="n">
         <v>392.71</v>
       </c>
       <c r="E210" s="18" t="n">
@@ -9330,7 +9353,7 @@
       <c r="C211" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D211" s="17" t="n">
+      <c r="D211" s="49" t="n">
         <v>322.47</v>
       </c>
       <c r="E211" s="18" t="n">
@@ -9370,7 +9393,7 @@
       <c r="C212" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D212" s="17" t="n">
+      <c r="D212" s="49" t="n">
         <v>319.21</v>
       </c>
       <c r="E212" s="18" t="n">
@@ -9410,7 +9433,7 @@
       <c r="C213" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D213" s="17" t="n">
+      <c r="D213" s="49" t="n">
         <v>108.55</v>
       </c>
       <c r="E213" s="18" t="n">
@@ -9450,7 +9473,7 @@
       <c r="C214" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D214" s="17" t="n">
+      <c r="D214" s="49" t="n">
         <v>318.79</v>
       </c>
       <c r="E214" s="18" t="n">
@@ -9490,7 +9513,7 @@
       <c r="C215" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D215" s="17" t="n">
+      <c r="D215" s="49" t="n">
         <v>471.89</v>
       </c>
       <c r="E215" s="18" t="n">
@@ -9530,7 +9553,7 @@
       <c r="C216" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D216" s="17" t="n">
+      <c r="D216" s="49" t="n">
         <v>318.92</v>
       </c>
       <c r="E216" s="18" t="n">
@@ -9570,7 +9593,7 @@
       <c r="C217" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D217" s="17" t="n">
+      <c r="D217" s="49" t="n">
         <v>211.35</v>
       </c>
       <c r="E217" s="18" t="n">
@@ -9610,7 +9633,7 @@
       <c r="C218" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D218" s="17" t="n">
+      <c r="D218" s="49" t="n">
         <v>167.48</v>
       </c>
       <c r="E218" s="18" t="n">
@@ -9650,7 +9673,7 @@
       <c r="C219" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D219" s="17" t="n">
+      <c r="D219" s="49" t="n">
         <v>150.35</v>
       </c>
       <c r="E219" s="18" t="n">
@@ -9690,7 +9713,7 @@
       <c r="C220" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D220" s="17" t="n">
+      <c r="D220" s="49" t="n">
         <v>140.13</v>
       </c>
       <c r="E220" s="18" t="n">
@@ -9730,7 +9753,7 @@
       <c r="C221" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D221" s="17" t="n">
+      <c r="D221" s="49" t="n">
         <v>64.91</v>
       </c>
       <c r="E221" s="18" t="n">
@@ -9770,7 +9793,7 @@
       <c r="C222" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D222" s="17" t="n">
+      <c r="D222" s="49" t="n">
         <v>31.71</v>
       </c>
       <c r="E222" s="18" t="n">
@@ -9810,7 +9833,7 @@
       <c r="C223" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D223" s="17" t="n">
+      <c r="D223" s="49" t="n">
         <v>40.93</v>
       </c>
       <c r="E223" s="18" t="n">
@@ -9850,7 +9873,7 @@
       <c r="C224" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D224" s="17" t="n">
+      <c r="D224" s="49" t="n">
         <v>10.53</v>
       </c>
       <c r="E224" s="18" t="n">
@@ -9890,7 +9913,7 @@
       <c r="C225" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D225" s="17" t="n">
+      <c r="D225" s="49" t="n">
         <v>1.32</v>
       </c>
       <c r="E225" s="18" t="n">
@@ -9930,7 +9953,7 @@
       <c r="C226" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D226" s="17" t="n">
+      <c r="D226" s="49" t="n">
         <v>320.85</v>
       </c>
       <c r="E226" s="18" t="n">
@@ -9970,7 +9993,7 @@
       <c r="C227" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D227" s="17" t="n">
+      <c r="D227" s="49" t="n">
         <v>8.42</v>
       </c>
       <c r="E227" s="18" t="n">
@@ -10011,7 +10034,7 @@
         <f>SUM(C195:C227)</f>
         <v/>
       </c>
-      <c r="D228" s="22">
+      <c r="D228" s="50">
         <f>SUM(D195:D227)</f>
         <v/>
       </c>
@@ -10020,7 +10043,7 @@
         <v/>
       </c>
       <c r="F228" s="23">
-        <f>SUM(F195:F227)</f>
+        <f>SUMIF(E195:E227,"&gt;0",F195:F227)</f>
         <v/>
       </c>
       <c r="G228" s="24">
@@ -10058,7 +10081,7 @@
       <c r="C229" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D229" s="17" t="n">
+      <c r="D229" s="49" t="n">
         <v>543.88</v>
       </c>
       <c r="E229" s="18" t="n">
@@ -10098,7 +10121,7 @@
       <c r="C230" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D230" s="17" t="n">
+      <c r="D230" s="49" t="n">
         <v>543.86</v>
       </c>
       <c r="E230" s="18" t="n">
@@ -10138,7 +10161,7 @@
       <c r="C231" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D231" s="17" t="n">
+      <c r="D231" s="49" t="n">
         <v>541.64</v>
       </c>
       <c r="E231" s="18" t="n">
@@ -10178,7 +10201,7 @@
       <c r="C232" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D232" s="17" t="n">
+      <c r="D232" s="49" t="n">
         <v>543.88</v>
       </c>
       <c r="E232" s="18" t="n">
@@ -10218,7 +10241,7 @@
       <c r="C233" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D233" s="17" t="n">
+      <c r="D233" s="49" t="n">
         <v>543.62</v>
       </c>
       <c r="E233" s="18" t="n">
@@ -10258,7 +10281,7 @@
       <c r="C234" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D234" s="17" t="n">
+      <c r="D234" s="49" t="n">
         <v>543.88</v>
       </c>
       <c r="E234" s="18" t="n">
@@ -10298,7 +10321,7 @@
       <c r="C235" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D235" s="17" t="n">
+      <c r="D235" s="49" t="n">
         <v>543.64</v>
       </c>
       <c r="E235" s="18" t="n">
@@ -10338,7 +10361,7 @@
       <c r="C236" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D236" s="17" t="n">
+      <c r="D236" s="49" t="n">
         <v>329.9</v>
       </c>
       <c r="E236" s="18" t="n">
@@ -10378,7 +10401,7 @@
       <c r="C237" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D237" s="17" t="n">
+      <c r="D237" s="49" t="n">
         <v>321.31</v>
       </c>
       <c r="E237" s="18" t="n">
@@ -10418,7 +10441,7 @@
       <c r="C238" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D238" s="17" t="n">
+      <c r="D238" s="49" t="n">
         <v>251.8</v>
       </c>
       <c r="E238" s="18" t="n">
@@ -10458,7 +10481,7 @@
       <c r="C239" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D239" s="17" t="n">
+      <c r="D239" s="49" t="n">
         <v>329.84</v>
       </c>
       <c r="E239" s="18" t="n">
@@ -10498,7 +10521,7 @@
       <c r="C240" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D240" s="17" t="n">
+      <c r="D240" s="49" t="n">
         <v>470.59</v>
       </c>
       <c r="E240" s="18" t="n">
@@ -10538,7 +10561,7 @@
       <c r="C241" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D241" s="17" t="n">
+      <c r="D241" s="49" t="n">
         <v>515.66</v>
       </c>
       <c r="E241" s="18" t="n">
@@ -10578,7 +10601,7 @@
       <c r="C242" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D242" s="17" t="n">
+      <c r="D242" s="49" t="n">
         <v>469.2</v>
       </c>
       <c r="E242" s="18" t="n">
@@ -10618,7 +10641,7 @@
       <c r="C243" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D243" s="17" t="n">
+      <c r="D243" s="49" t="n">
         <v>538.42</v>
       </c>
       <c r="E243" s="18" t="n">
@@ -10658,7 +10681,7 @@
       <c r="C244" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D244" s="17" t="n">
+      <c r="D244" s="49" t="n">
         <v>392.71</v>
       </c>
       <c r="E244" s="18" t="n">
@@ -10698,7 +10721,7 @@
       <c r="C245" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D245" s="17" t="n">
+      <c r="D245" s="49" t="n">
         <v>470.57</v>
       </c>
       <c r="E245" s="18" t="n">
@@ -10738,7 +10761,7 @@
       <c r="C246" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D246" s="17" t="n">
+      <c r="D246" s="49" t="n">
         <v>214.44</v>
       </c>
       <c r="E246" s="18" t="n">
@@ -10778,7 +10801,7 @@
       <c r="C247" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D247" s="17" t="n">
+      <c r="D247" s="49" t="n">
         <v>322.62</v>
       </c>
       <c r="E247" s="18" t="n">
@@ -10818,7 +10841,7 @@
       <c r="C248" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D248" s="17" t="n">
+      <c r="D248" s="49" t="n">
         <v>345.05</v>
       </c>
       <c r="E248" s="18" t="n">
@@ -10858,7 +10881,7 @@
       <c r="C249" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D249" s="17" t="n">
+      <c r="D249" s="49" t="n">
         <v>321.71</v>
       </c>
       <c r="E249" s="18" t="n">
@@ -10898,7 +10921,7 @@
       <c r="C250" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D250" s="17" t="n">
+      <c r="D250" s="49" t="n">
         <v>319.09</v>
       </c>
       <c r="E250" s="18" t="n">
@@ -10938,7 +10961,7 @@
       <c r="C251" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D251" s="17" t="n">
+      <c r="D251" s="49" t="n">
         <v>320.02</v>
       </c>
       <c r="E251" s="18" t="n">
@@ -10978,7 +11001,7 @@
       <c r="C252" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D252" s="17" t="n">
+      <c r="D252" s="49" t="n">
         <v>180.65</v>
       </c>
       <c r="E252" s="18" t="n">
@@ -11018,7 +11041,7 @@
       <c r="C253" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D253" s="17" t="n">
+      <c r="D253" s="49" t="n">
         <v>108.53</v>
       </c>
       <c r="E253" s="18" t="n">
@@ -11058,7 +11081,7 @@
       <c r="C254" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D254" s="17" t="n">
+      <c r="D254" s="49" t="n">
         <v>317.88</v>
       </c>
       <c r="E254" s="18" t="n">
@@ -11098,7 +11121,7 @@
       <c r="C255" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D255" s="17" t="n">
+      <c r="D255" s="49" t="n">
         <v>248.18</v>
       </c>
       <c r="E255" s="18" t="n">
@@ -11138,7 +11161,7 @@
       <c r="C256" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D256" s="17" t="n">
+      <c r="D256" s="49" t="n">
         <v>221.4</v>
       </c>
       <c r="E256" s="18" t="n">
@@ -11178,7 +11201,7 @@
       <c r="C257" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D257" s="17" t="n">
+      <c r="D257" s="49" t="n">
         <v>189.86</v>
       </c>
       <c r="E257" s="18" t="n">
@@ -11218,7 +11241,7 @@
       <c r="C258" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D258" s="17" t="n">
+      <c r="D258" s="49" t="n">
         <v>107.94</v>
       </c>
       <c r="E258" s="18" t="n">
@@ -11258,7 +11281,7 @@
       <c r="C259" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D259" s="17" t="n">
+      <c r="D259" s="49" t="n">
         <v>114.09</v>
       </c>
       <c r="E259" s="18" t="n">
@@ -11298,7 +11321,7 @@
       <c r="C260" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D260" s="17" t="n">
+      <c r="D260" s="49" t="n">
         <v>94.16</v>
       </c>
       <c r="E260" s="18" t="n">
@@ -11338,7 +11361,7 @@
       <c r="C261" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D261" s="17" t="n">
+      <c r="D261" s="49" t="n">
         <v>131.65</v>
       </c>
       <c r="E261" s="18" t="n">
@@ -11378,7 +11401,7 @@
       <c r="C262" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D262" s="17" t="n">
+      <c r="D262" s="49" t="n">
         <v>83.45999999999999</v>
       </c>
       <c r="E262" s="18" t="n">
@@ -11418,7 +11441,7 @@
       <c r="C263" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D263" s="17" t="n">
+      <c r="D263" s="49" t="n">
         <v>38.19</v>
       </c>
       <c r="E263" s="18" t="n">
@@ -11458,7 +11481,7 @@
       <c r="C264" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D264" s="17" t="n">
+      <c r="D264" s="49" t="n">
         <v>5.04</v>
       </c>
       <c r="E264" s="18" t="n">
@@ -11499,7 +11522,7 @@
         <f>SUM(C229:C264)</f>
         <v/>
       </c>
-      <c r="D265" s="22">
+      <c r="D265" s="50">
         <f>SUM(D229:D264)</f>
         <v/>
       </c>
@@ -11508,7 +11531,7 @@
         <v/>
       </c>
       <c r="F265" s="23">
-        <f>SUM(F229:F264)</f>
+        <f>SUMIF(E229:E264,"&gt;0",F229:F264)</f>
         <v/>
       </c>
       <c r="G265" s="24">
@@ -11543,7 +11566,7 @@
         <f>C43+C84+C130+C162+C194+C228+C265</f>
         <v/>
       </c>
-      <c r="D266" s="27">
+      <c r="D266" s="51">
         <f>D43+D84+D130+D162+D194+D228+D265</f>
         <v/>
       </c>
@@ -11621,7 +11644,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="30" t="inlineStr">
         <is>
@@ -11629,7 +11651,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -13331,7 +13352,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -36376,7 +36396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="B1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -36391,7 +36411,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="34" customHeight="1">
       <c r="B3" s="44" t="inlineStr">
         <is>
